--- a/tests/gold-project/outputs/reports/cast_scene.xlsx
+++ b/tests/gold-project/outputs/reports/cast_scene.xlsx
@@ -40,7 +40,7 @@
     <t>3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 23, 25, 26, 27, 28, 29, 30, 32, 34, 36, 39, 40, 41, 42, 43, 44, 45</t>
   </si>
   <si>
-    <t>Shoot Day 12 · Sat 23 Jan 2027; Shoot Day 3 · Wed 13 Jan 2027; Shoot Day 4 · Thu 14 Jan 2027; Shoot Day 7 · Mon 18 Jan 2027; Shoot Day 10 · Thu 21 Jan 2027; Shoot Day 5 · Fri 15 Jan 2027; Shoot Day 2 · Tue 12 Jan 2027; Shoot Day 6 · Sat 16 Jan 2027; Shoot Day 11 · Fri 22 Jan 2027; Shoot Day 8 · Tue 19 Jan 2027; Shoot Day 1 · Mon 11 Jan 2027; Shoot Day 9 · Wed 20 Jan 2027; Shoot Day 14 · Tue 26 Jan 2027</t>
+    <t>Shoot Day 1 · Mon 11 Jan 2027; Shoot Day 2 · Tue 12 Jan 2027; Shoot Day 3 · Wed 13 Jan 2027; Shoot Day 4 · Thu 14 Jan 2027; Shoot Day 5 · Fri 15 Jan 2027; Shoot Day 6 · Sat 16 Jan 2027; Shoot Day 7 · Mon 18 Jan 2027; Shoot Day 8 · Tue 19 Jan 2027; Shoot Day 9 · Wed 20 Jan 2027; Shoot Day 10 · Thu 21 Jan 2027; Shoot Day 11 · Fri 22 Jan 2027; Shoot Day 12 · Sat 23 Jan 2027; Shoot Day 14 · Tue 26 Jan 2027</t>
   </si>
   <si>
     <t>K. P. Gopinathan</t>
@@ -52,7 +52,7 @@
     <t>5, 6, 10, 15, 25, 26, 39, 40, 42, 45</t>
   </si>
   <si>
-    <t>Shoot Day 3 · Wed 13 Jan 2027; Shoot Day 4 · Thu 14 Jan 2027; Shoot Day 8 · Tue 19 Jan 2027; Shoot Day 12 · Sat 23 Jan 2027; Shoot Day 9 · Wed 20 Jan 2027; Shoot Day 14 · Tue 26 Jan 2027</t>
+    <t>Shoot Day 3 · Wed 13 Jan 2027; Shoot Day 4 · Thu 14 Jan 2027; Shoot Day 8 · Tue 19 Jan 2027; Shoot Day 9 · Wed 20 Jan 2027; Shoot Day 12 · Sat 23 Jan 2027; Shoot Day 14 · Tue 26 Jan 2027</t>
   </si>
   <si>
     <t>Sabitha Rasheed</t>
@@ -64,7 +64,7 @@
     <t>3, 6, 9, 13, 14, 16, 18, 20, 21, 23, 24, 34, 38, 40, 42, 43</t>
   </si>
   <si>
-    <t>Shoot Day 12 · Sat 23 Jan 2027; Shoot Day 4 · Thu 14 Jan 2027; Shoot Day 5 · Fri 15 Jan 2027; Shoot Day 6 · Sat 16 Jan 2027; Shoot Day 10 · Thu 21 Jan 2027; Shoot Day 7 · Mon 18 Jan 2027; Shoot Day 8 · Tue 19 Jan 2027; Shoot Day 9 · Wed 20 Jan 2027; Shoot Day 14 · Tue 26 Jan 2027</t>
+    <t>Shoot Day 4 · Thu 14 Jan 2027; Shoot Day 5 · Fri 15 Jan 2027; Shoot Day 6 · Sat 16 Jan 2027; Shoot Day 7 · Mon 18 Jan 2027; Shoot Day 8 · Tue 19 Jan 2027; Shoot Day 9 · Wed 20 Jan 2027; Shoot Day 10 · Thu 21 Jan 2027; Shoot Day 12 · Sat 23 Jan 2027; Shoot Day 14 · Tue 26 Jan 2027</t>
   </si>
   <si>
     <t>Not cast yet</t>
@@ -97,7 +97,7 @@
     <t>2, 17, 29, 30, 31, 32, 33, 38, 40</t>
   </si>
   <si>
-    <t>Shoot Day 2 · Tue 12 Jan 2027; Shoot Day 5 · Fri 15 Jan 2027; Shoot Day 1 · Mon 11 Jan 2027; Shoot Day 11 · Fri 22 Jan 2027; Shoot Day 9 · Wed 20 Jan 2027</t>
+    <t>Shoot Day 1 · Mon 11 Jan 2027; Shoot Day 2 · Tue 12 Jan 2027; Shoot Day 5 · Fri 15 Jan 2027; Shoot Day 9 · Wed 20 Jan 2027; Shoot Day 11 · Fri 22 Jan 2027</t>
   </si>
   <si>
     <t>Reshmi Pillai</t>
@@ -109,7 +109,7 @@
     <t>5, 19, 31, 32, 40, 42</t>
   </si>
   <si>
-    <t>Shoot Day 3 · Wed 13 Jan 2027; Shoot Day 11 · Fri 22 Jan 2027; Shoot Day 9 · Wed 20 Jan 2027; Shoot Day 14 · Tue 26 Jan 2027</t>
+    <t>Shoot Day 3 · Wed 13 Jan 2027; Shoot Day 9 · Wed 20 Jan 2027; Shoot Day 11 · Fri 22 Jan 2027; Shoot Day 14 · Tue 26 Jan 2027</t>
   </si>
   <si>
     <t>Divya Mathew</t>
@@ -121,7 +121,7 @@
     <t>1, 2, 4, 10, 16, 19, 33, 34, 35, 40, 41</t>
   </si>
   <si>
-    <t>Shoot Day 13 · Mon 25 Jan 2027; Shoot Day 2 · Tue 12 Jan 2027; Shoot Day 12 · Sat 23 Jan 2027; Shoot Day 4 · Thu 14 Jan 2027; Shoot Day 6 · Sat 16 Jan 2027; Shoot Day 11 · Fri 22 Jan 2027; Shoot Day 9 · Wed 20 Jan 2027; Shoot Day 3 · Wed 13 Jan 2027</t>
+    <t>Shoot Day 2 · Tue 12 Jan 2027; Shoot Day 3 · Wed 13 Jan 2027; Shoot Day 4 · Thu 14 Jan 2027; Shoot Day 6 · Sat 16 Jan 2027; Shoot Day 9 · Wed 20 Jan 2027; Shoot Day 11 · Fri 22 Jan 2027; Shoot Day 12 · Sat 23 Jan 2027; Shoot Day 13 · Mon 25 Jan 2027</t>
   </si>
   <si>
     <t>Gauri Krishna</t>
@@ -175,7 +175,7 @@
     <t>9, 11, 12, 13, 14, 16, 21, 23, 28, 29, 34, 38, 40, 41, 43</t>
   </si>
   <si>
-    <t>Shoot Day 5 · Fri 15 Jan 2027; Shoot Day 2 · Tue 12 Jan 2027; Shoot Day 3 · Wed 13 Jan 2027; Shoot Day 6 · Sat 16 Jan 2027; Shoot Day 7 · Mon 18 Jan 2027; Shoot Day 8 · Tue 19 Jan 2027; Shoot Day 1 · Mon 11 Jan 2027; Shoot Day 9 · Wed 20 Jan 2027; Shoot Day 14 · Tue 26 Jan 2027</t>
+    <t>Shoot Day 1 · Mon 11 Jan 2027; Shoot Day 2 · Tue 12 Jan 2027; Shoot Day 3 · Wed 13 Jan 2027; Shoot Day 5 · Fri 15 Jan 2027; Shoot Day 6 · Sat 16 Jan 2027; Shoot Day 7 · Mon 18 Jan 2027; Shoot Day 8 · Tue 19 Jan 2027; Shoot Day 9 · Wed 20 Jan 2027; Shoot Day 14 · Tue 26 Jan 2027</t>
   </si>
   <si>
     <t>Karan Shetty</t>
@@ -199,7 +199,7 @@
     <t>7, 8, 18, 23, 25, 26, 27, 28, 29, 30, 36, 37, 38, 40, 42</t>
   </si>
   <si>
-    <t>Shoot Day 7 · Mon 18 Jan 2027; Shoot Day 10 · Thu 21 Jan 2027; Shoot Day 8 · Tue 19 Jan 2027; Shoot Day 12 · Sat 23 Jan 2027; Shoot Day 1 · Mon 11 Jan 2027; Shoot Day 5 · Fri 15 Jan 2027; Shoot Day 9 · Wed 20 Jan 2027; Shoot Day 14 · Tue 26 Jan 2027</t>
+    <t>Shoot Day 1 · Mon 11 Jan 2027; Shoot Day 5 · Fri 15 Jan 2027; Shoot Day 7 · Mon 18 Jan 2027; Shoot Day 8 · Tue 19 Jan 2027; Shoot Day 9 · Wed 20 Jan 2027; Shoot Day 10 · Thu 21 Jan 2027; Shoot Day 12 · Sat 23 Jan 2027; Shoot Day 14 · Tue 26 Jan 2027</t>
   </si>
   <si>
     <t>Thampi Cherian</t>
@@ -211,7 +211,7 @@
     <t>1, 34, 35, 36, 40</t>
   </si>
   <si>
-    <t>Shoot Day 13 · Mon 25 Jan 2027; Shoot Day 6 · Sat 16 Jan 2027; Shoot Day 10 · Thu 21 Jan 2027; Shoot Day 9 · Wed 20 Jan 2027</t>
+    <t>Shoot Day 6 · Sat 16 Jan 2027; Shoot Day 9 · Wed 20 Jan 2027; Shoot Day 10 · Thu 21 Jan 2027; Shoot Day 13 · Mon 25 Jan 2027</t>
   </si>
   <si>
     <t>Ameya Suresh</t>
@@ -884,7 +884,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="200" verticalDpi="200"/>
   <headerFooter>
-    <oddFooter>&amp;CCreated with OpenFrame Studio</oddFooter>
+    <oddFooter>&amp;CCreated using OpenFrame</oddFooter>
   </headerFooter>
 </worksheet>
 </file>